--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486780_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486780_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6611</v>
+        <v>0.5678</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4251</v>
+        <v>0.9841</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7639</v>
+        <v>-0.4163</v>
       </c>
       <c r="G2" t="n">
         <v>-0.0649</v>
@@ -610,13 +610,13 @@
         <v>0.5792</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7759</v>
+        <v>0.6826</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9302</v>
+        <v>0.4892</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1543</v>
+        <v>0.1934</v>
       </c>
       <c r="V2" t="n">
         <v>-0.243</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. ANDRADE ROSSI</t>
+          <t>A. VERA PICAZO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.6197</v>
+        <v>-2.1617</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3713</v>
+        <v>2.1706</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.2483</v>
+        <v>-4.3323</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.7525</v>
+        <v>1.6349</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.1037</v>
+        <v>-1.0689</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6489</v>
+        <v>2.7038</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4355</v>
+        <v>5.1812</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3112</v>
+        <v>1.5527</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1244</v>
+        <v>3.6285</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.1881</v>
+        <v>-3.5463</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.4148</v>
+        <v>-2.6216</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7732</v>
+        <v>-0.9247</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1931</v>
+        <v>-3.6685</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1585</v>
+        <v>-4.0546</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9654</v>
+        <v>0.3862</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.23</v>
+        <v>-0.4137</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.4899</v>
+        <v>-0.4692</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2599</v>
+        <v>0.0555</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5559</v>
+        <v>0.2856</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8415</v>
+        <v>1.5133</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2856</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. VERA PICAZO</t>
+          <t>A. ANDRADE ROSSI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.0334</v>
+        <v>-2.1619</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6465</v>
+        <v>0.3596</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.68</v>
+        <v>-2.5215</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6349</v>
+        <v>-2.7525</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.0689</v>
+        <v>-2.1037</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7038</v>
+        <v>-0.6489</v>
       </c>
       <c r="J4" t="n">
-        <v>5.1812</v>
+        <v>0.4355</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5527</v>
+        <v>0.3112</v>
       </c>
       <c r="L4" t="n">
-        <v>3.6285</v>
+        <v>0.1244</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.5463</v>
+        <v>-3.1881</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.6216</v>
+        <v>-2.4148</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9247</v>
+        <v>-0.7732</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.6685</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.0546</v>
+        <v>-1.1585</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3862</v>
+        <v>0.9654</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2854</v>
+        <v>-0.7722</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9933</v>
+        <v>-0.759</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2922</v>
+        <v>-0.0132</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2856</v>
+        <v>1.5559</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5133</v>
+        <v>1.8415</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.4836</v>
+        <v>-2.9624</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2063</v>
+        <v>-0.5857</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.2774</v>
+        <v>-2.3767</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2662</v>
@@ -844,13 +844,13 @@
         <v>1.1585</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6383</v>
+        <v>-1.1171</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.6003</v>
+        <v>-0.9797</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.038</v>
+        <v>-0.1373</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6138</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.7534</v>
+        <v>-3.5258</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.6495</v>
+        <v>-2.5461</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1039</v>
+        <v>-0.9797</v>
       </c>
       <c r="G6" t="n">
         <v>-2.2363</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5516</v>
+        <v>-0.3241</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3311</v>
+        <v>-0.2277</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2206</v>
+        <v>-0.0964</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.4424</v>
+        <v>-4.3059</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.3326</v>
+        <v>-3.0223</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1098</v>
+        <v>-1.2836</v>
       </c>
       <c r="G7" t="n">
         <v>-4.0082</v>
@@ -1000,13 +1000,13 @@
         <v>0.9654</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1639</v>
+        <v>-1.0274</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0485</v>
+        <v>-0.7382</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1154</v>
+        <v>-0.2892</v>
       </c>
       <c r="V7" t="n">
         <v>-0.0426</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-8.922000000000001</v>
+        <v>-8.5343</v>
       </c>
       <c r="E8" t="n">
-        <v>-7.4714</v>
+        <v>-7.2576</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4506</v>
+        <v>-1.2767</v>
       </c>
       <c r="G8" t="n">
         <v>-5.7445</v>
@@ -1078,13 +1078,13 @@
         <v>0.9654</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7946</v>
+        <v>-0.407</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4142</v>
+        <v>-0.2004</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3804</v>
+        <v>-0.2066</v>
       </c>
       <c r="V8" t="n">
         <v>0.8995</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-9.2522</v>
+        <v>-10.2093</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.8125</v>
+        <v>-5.3226</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.4397</v>
+        <v>-4.8867</v>
       </c>
       <c r="G9" t="n">
         <v>-5.0468</v>
@@ -1156,13 +1156,13 @@
         <v>0.7723</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4744</v>
+        <v>-0.4827</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2201</v>
+        <v>-0.29</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2543</v>
+        <v>-0.1927</v>
       </c>
       <c r="V9" t="n">
         <v>-2.1698</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-33.8456</v>
+        <v>-33.29349999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-15.772</v>
+        <v>-15.22</v>
       </c>
       <c r="F10" t="n">
-        <v>-18.0736</v>
+        <v>-18.0735</v>
       </c>
       <c r="G10" t="n">
         <v>-18.4845</v>
@@ -1210,7 +1210,7 @@
         <v>0.5257999999999985</v>
       </c>
       <c r="K10" t="n">
-        <v>1.384499999999999</v>
+        <v>1.3845</v>
       </c>
       <c r="L10" t="n">
         <v>-0.8584999999999998</v>
@@ -1231,19 +1231,19 @@
         <v>-16.4117</v>
       </c>
       <c r="R10" t="n">
-        <v>5.792400000000001</v>
+        <v>5.7924</v>
       </c>
       <c r="S10" t="n">
-        <v>-4.4135</v>
+        <v>-3.8616</v>
       </c>
       <c r="T10" t="n">
-        <v>-3.726999999999999</v>
+        <v>-3.175</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6866999999999999</v>
+        <v>-0.6864999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3282</v>
+        <v>-0.3281999999999998</v>
       </c>
       <c r="W10" t="n">
         <v>3.8409</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>10.2591</v>
+        <v>9.431699999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>8.065899999999999</v>
+        <v>7.2385</v>
       </c>
       <c r="F11" t="n">
         <v>2.1932</v>
@@ -1312,10 +1312,10 @@
         <v>2.1239</v>
       </c>
       <c r="S11" t="n">
-        <v>2.0961</v>
+        <v>1.2687</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2682</v>
+        <v>0.4409</v>
       </c>
       <c r="U11" t="n">
         <v>0.8279</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. CASTELANOS POLA</t>
+          <t>M. OLIVA I CAMPABADAL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.2098</v>
+        <v>6.2967</v>
       </c>
       <c r="E12" t="n">
-        <v>3.7428</v>
+        <v>4.856</v>
       </c>
       <c r="F12" t="n">
-        <v>2.467</v>
+        <v>1.4407</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3492</v>
+        <v>3.5932</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0893</v>
+        <v>2.3657</v>
       </c>
       <c r="I12" t="n">
-        <v>3.4384</v>
+        <v>1.2275</v>
       </c>
       <c r="J12" t="n">
-        <v>1.6532</v>
+        <v>3.7802</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9510999999999999</v>
+        <v>2.435</v>
       </c>
       <c r="L12" t="n">
-        <v>2.6043</v>
+        <v>1.3451</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6959</v>
+        <v>-0.1869</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1382</v>
+        <v>-0.0693</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8341</v>
+        <v>-0.1176</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1585</v>
+        <v>1.5446</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1585</v>
+        <v>1.5446</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2042</v>
+        <v>-0.0689</v>
       </c>
       <c r="T12" t="n">
-        <v>0.248</v>
+        <v>-0.1519</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0438</v>
+        <v>0.083</v>
       </c>
       <c r="V12" t="n">
-        <v>2.498</v>
+        <v>1.2277</v>
       </c>
       <c r="W12" t="n">
-        <v>1.8415</v>
+        <v>1.2277</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.9467</v>
+        <v>6.0791</v>
       </c>
       <c r="E13" t="n">
-        <v>5.8438</v>
+        <v>6.0506</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1029</v>
+        <v>0.0284</v>
       </c>
       <c r="G13" t="n">
         <v>6.5745</v>
@@ -1468,13 +1468,13 @@
         <v>0.5792</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0219</v>
+        <v>0.1105</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1104</v>
+        <v>0.0965</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0885</v>
+        <v>0.014</v>
       </c>
       <c r="V13" t="n">
         <v>-1.1851</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. OLIVA I CAMPABADAL</t>
+          <t>A. CASTELANOS POLA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.9408</v>
+        <v>5.9781</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6491</v>
+        <v>3.536</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2917</v>
+        <v>2.4422</v>
       </c>
       <c r="G14" t="n">
-        <v>3.5932</v>
+        <v>2.3492</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3657</v>
+        <v>-1.0893</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2275</v>
+        <v>3.4384</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7802</v>
+        <v>1.6532</v>
       </c>
       <c r="K14" t="n">
-        <v>2.435</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3451</v>
+        <v>2.6043</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1869</v>
+        <v>0.6959</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0693</v>
+        <v>-0.1382</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1176</v>
+        <v>0.8341</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5446</v>
+        <v>1.1585</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5446</v>
+        <v>1.1585</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4247</v>
+        <v>-0.0275</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3587</v>
+        <v>0.0412</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.066</v>
+        <v>-0.0687</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2277</v>
+        <v>2.498</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2277</v>
+        <v>1.8415</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4117</v>
+        <v>2.667</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5022</v>
+        <v>0.8817</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9095</v>
+        <v>1.7853</v>
       </c>
       <c r="G15" t="n">
         <v>0.43</v>
@@ -1624,13 +1624,13 @@
         <v>1.9308</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3791</v>
+        <v>0.6344</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7995</v>
+        <v>0.179</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5796</v>
+        <v>0.4555</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3282</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2366</v>
+        <v>2.4146</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4565</v>
+        <v>1.56</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7801</v>
+        <v>0.8546</v>
       </c>
       <c r="G16" t="n">
         <v>2.6531</v>
@@ -1702,13 +1702,13 @@
         <v>1.1585</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2813</v>
+        <v>-0.1034</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3036</v>
+        <v>-0.2001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0223</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3282</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. KASA</t>
+          <t>N. CEBRIAN HERNANDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7988</v>
+        <v>1.7906</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2072</v>
+        <v>-0.4291</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0059</v>
+        <v>2.2197</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4659</v>
+        <v>0.8667</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6342</v>
+        <v>-0.4898</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.1001</v>
+        <v>1.3565</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8304</v>
+        <v>0.7849</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1521</v>
+        <v>-0.2823</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.9825</v>
+        <v>1.0671</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3645</v>
+        <v>0.0818</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4821</v>
+        <v>-0.2075</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1176</v>
+        <v>0.2893</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7723</v>
+        <v>0.5792</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.1585</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9308</v>
+        <v>1.7377</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4344</v>
+        <v>0.3447</v>
       </c>
       <c r="T17" t="n">
-        <v>0.496</v>
+        <v>-0.0555</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9383</v>
+        <v>0.4002</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9421</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. CEBRIAN HERNANDEZ</t>
+          <t>J. KASA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6404</v>
+        <v>0.447</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2565</v>
+        <v>-1.3106</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8969</v>
+        <v>1.7576</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8667</v>
+        <v>-0.4659</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4898</v>
+        <v>1.6342</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3565</v>
+        <v>-2.1001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7849</v>
+        <v>-0.8304</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2823</v>
+        <v>1.1521</v>
       </c>
       <c r="L18" t="n">
-        <v>1.0671</v>
+        <v>-1.9825</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0818</v>
+        <v>0.3645</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2075</v>
+        <v>0.4821</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2893</v>
+        <v>-0.1176</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5792</v>
+        <v>0.7723</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.1585</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7377</v>
+        <v>1.9308</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8055</v>
+        <v>1.0826</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8829</v>
+        <v>0.3926</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0774</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.9421</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. LOPEZ USO</t>
+          <t>R. ACIU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0251</v>
+        <v>-0.0828</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6058</v>
+        <v>-0.0552</v>
       </c>
       <c r="F19" t="n">
-        <v>1.631</v>
+        <v>-0.0276</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5678</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.607</v>
+        <v>-0.2069</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9608</v>
+        <v>0.1379</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.4497</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8823</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5674</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1181</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2753</v>
+        <v>-0.2069</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3934</v>
+        <v>0.1379</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1931</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1585</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3515</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1143</v>
+        <v>-0.0138</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7168</v>
+        <v>-0.0552</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3975</v>
+        <v>0.0414</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. ACIU</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1077</v>
+        <v>-0.1839</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0552</v>
+        <v>-1.4901</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0525</v>
+        <v>1.3061</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-1.0249</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2069</v>
+        <v>1.0616</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1379</v>
+        <v>-2.0865</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.3685</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.9245</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-1.293</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.6564</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2069</v>
+        <v>0.1371</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1379</v>
+        <v>-0.7935</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.5446</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1585</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.7031</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0386</v>
+        <v>0.5241</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0552</v>
+        <v>-0.2487</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0166</v>
+        <v>0.7728</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. NAVARRO ANTON</t>
+          <t>P. LOPEZ USO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6041</v>
+        <v>-0.4134</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7447</v>
+        <v>-2.0195</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1406</v>
+        <v>1.6061</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7585</v>
+        <v>-1.5678</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2069</v>
+        <v>-0.607</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5516</v>
+        <v>-0.9608</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6895</v>
+        <v>-1.4497</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>-0.8823</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6895</v>
+        <v>-0.5674</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.1181</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2069</v>
+        <v>0.2753</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1379</v>
+        <v>-0.3934</v>
       </c>
       <c r="P21" t="n">
         <v>0.1931</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1585</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1931</v>
+        <v>1.3515</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0386</v>
+        <v>0.6757</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0552</v>
+        <v>0.3031</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0166</v>
+        <v>0.3727</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>F. NAVARRO ANTON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.912</v>
+        <v>-0.5792</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3175</v>
+        <v>-0.7447</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4055</v>
+        <v>0.1654</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0249</v>
+        <v>-0.7585</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0616</v>
+        <v>-0.2069</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0865</v>
+        <v>-0.5516</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3685</v>
+        <v>-0.6895</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9245</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.293</v>
+        <v>-0.6895</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6564</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1371</v>
+        <v>-0.2069</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7935</v>
+        <v>0.1379</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5446</v>
+        <v>0.1931</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1585</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7031</v>
+        <v>0.1931</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.204</v>
+        <v>-0.0138</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0761</v>
+        <v>-0.0552</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8721</v>
+        <v>0.0414</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>33.8452</v>
+        <v>33.8455</v>
       </c>
       <c r="E23" t="n">
-        <v>18.0734</v>
+        <v>18.0736</v>
       </c>
       <c r="F23" t="n">
-        <v>15.7718</v>
+        <v>15.7717</v>
       </c>
       <c r="G23" t="n">
         <v>18.4846</v>
@@ -2218,7 +2218,7 @@
         <v>13.104</v>
       </c>
       <c r="I23" t="n">
-        <v>5.3805</v>
+        <v>5.380500000000001</v>
       </c>
       <c r="J23" t="n">
         <v>19.0103</v>
@@ -2227,16 +2227,16 @@
         <v>14.4884</v>
       </c>
       <c r="L23" t="n">
-        <v>4.521799999999999</v>
+        <v>4.5218</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5257000000000001</v>
+        <v>-0.5257000000000002</v>
       </c>
       <c r="N23" t="n">
         <v>-1.3844</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8585999999999999</v>
+        <v>0.8586000000000001</v>
       </c>
       <c r="P23" t="n">
         <v>10.6193</v>
@@ -2248,16 +2248,16 @@
         <v>16.4117</v>
       </c>
       <c r="S23" t="n">
-        <v>4.4135</v>
+        <v>4.4133</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6864000000000001</v>
+        <v>0.6867</v>
       </c>
       <c r="U23" t="n">
-        <v>3.727</v>
+        <v>3.7269</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3282000000000003</v>
+        <v>0.3282000000000002</v>
       </c>
       <c r="W23" t="n">
         <v>4.169</v>
